--- a/Backtest/02-08-19/NASDAQstock_02-08-19period252RS90.xlsx
+++ b/Backtest/02-08-19/NASDAQstock_02-08-19period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="133">
   <si>
     <t>Stock</t>
   </si>
@@ -127,337 +127,292 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>CGAU</t>
-  </si>
-  <si>
-    <t>PCTY</t>
-  </si>
-  <si>
-    <t>TTEC</t>
-  </si>
-  <si>
-    <t>RNR</t>
-  </si>
-  <si>
-    <t>PODD</t>
-  </si>
-  <si>
-    <t>BALL</t>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>CTRE</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>AMED</t>
+  </si>
+  <si>
+    <t>TPIC</t>
+  </si>
+  <si>
+    <t>SUI</t>
   </si>
   <si>
     <t>OSIS</t>
   </si>
   <si>
-    <t>ENPH</t>
-  </si>
-  <si>
-    <t>SMG</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t>ARWR</t>
-  </si>
-  <si>
-    <t>EPAM</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>BOOT</t>
-  </si>
-  <si>
-    <t>PAGS</t>
-  </si>
-  <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>NGL</t>
-  </si>
-  <si>
-    <t>OLED</t>
-  </si>
-  <si>
-    <t>SUN</t>
-  </si>
-  <si>
-    <t>EXPO</t>
-  </si>
-  <si>
-    <t>HURN</t>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>FBP</t>
+  </si>
+  <si>
+    <t>CQP</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>SPSC</t>
+  </si>
+  <si>
+    <t>IPAR</t>
+  </si>
+  <si>
+    <t>TRIP</t>
+  </si>
+  <si>
+    <t>TKO</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>MRK</t>
+  </si>
+  <si>
+    <t>EVTC</t>
+  </si>
+  <si>
+    <t>MTCH</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>VEEV</t>
   </si>
   <si>
     <t>BAH</t>
   </si>
   <si>
-    <t>CYBR</t>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>BPOP</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>TSCO</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>GLOB</t>
   </si>
   <si>
     <t>HEI</t>
   </si>
   <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>DAY</t>
-  </si>
-  <si>
-    <t>ELP</t>
-  </si>
-  <si>
-    <t>ENSG</t>
-  </si>
-  <si>
-    <t>NYT</t>
-  </si>
-  <si>
-    <t>AQN</t>
-  </si>
-  <si>
-    <t>KEYS</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>YETI</t>
-  </si>
-  <si>
-    <t>SNN</t>
-  </si>
-  <si>
-    <t>EVTC</t>
-  </si>
-  <si>
-    <t>HEI-A</t>
-  </si>
-  <si>
-    <t>KNSL</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>NEO</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>LULU</t>
+    <t>NNN</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-10-30</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-10-29</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-10-31</t>
-  </si>
-  <si>
-    <t>2019-08-26</t>
-  </si>
-  <si>
-    <t>2019-11-06</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-11-04</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-10-22</t>
-  </si>
-  <si>
-    <t>2019-10-17</t>
-  </si>
-  <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-11-07</t>
-  </si>
-  <si>
-    <t>2019-08-14</t>
-  </si>
-  <si>
-    <t>2025-02-25</t>
-  </si>
-  <si>
-    <t>2019-10-21</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
+    <t>MV</t>
+  </si>
+  <si>
+    <t>2019-02-14</t>
+  </si>
+  <si>
+    <t>2019-02-13</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2019-02-27</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>2019-02-20</t>
+  </si>
+  <si>
+    <t>2019-04-30</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-02-21</t>
+  </si>
+  <si>
+    <t>2019-04-24</t>
+  </si>
+  <si>
+    <t>2019-02-26</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-02-12</t>
+  </si>
+  <si>
+    <t>2019-03-04</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>2019-02-11</t>
+  </si>
+  <si>
+    <t>2019-05-01</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-04-18</t>
+  </si>
+  <si>
+    <t>2019-02-25</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Basic Materials</t>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Financial Services</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
   </si>
   <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
     <t>Utilities</t>
   </si>
   <si>
-    <t>Communication Services</t>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>REIT - Healthcare Facilities</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Medical Care Facilities</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>REIT - Residential</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Specialty Retail</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Insurance Brokers</t>
+  </si>
+  <si>
+    <t>Banks - Regional</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Publishing</t>
   </si>
   <si>
     <t>Software - Application</t>
   </si>
   <si>
-    <t>Gold</t>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Utilities - Diversified</t>
+  </si>
+  <si>
+    <t>Health Information Services</t>
+  </si>
+  <si>
+    <t>Consulting Services</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
   </si>
   <si>
     <t>Information Technology Services</t>
   </si>
   <si>
-    <t>Insurance - Reinsurance</t>
-  </si>
-  <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Packaging &amp; Containers</t>
-  </si>
-  <si>
-    <t>Electronic Components</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Agricultural Inputs</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>Apparel Retail</t>
-  </si>
-  <si>
-    <t>Software - Infrastructure</t>
-  </si>
-  <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
-    <t>Internet Retail</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Refining &amp; Marketing</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Consulting Services</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Health Information Services</t>
-  </si>
-  <si>
-    <t>Utilities - Diversified</t>
-  </si>
-  <si>
-    <t>Medical Care Facilities</t>
-  </si>
-  <si>
-    <t>Publishing</t>
-  </si>
-  <si>
-    <t>Utilities - Renewable</t>
-  </si>
-  <si>
-    <t>Scientific &amp; Technical Instruments</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Leisure</t>
-  </si>
-  <si>
-    <t>Insurance - Property &amp; Casualty</t>
-  </si>
-  <si>
-    <t>Credit Services</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
+    <t>REIT - Retail</t>
   </si>
 </sst>
 </file>
@@ -815,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -936,49 +891,49 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>90.61650045330916</v>
+        <v>93.57260145437485</v>
       </c>
       <c r="C2">
-        <v>920</v>
+        <v>1468</v>
       </c>
       <c r="D2">
-        <v>268.56</v>
+        <v>176.79</v>
       </c>
       <c r="E2">
-        <v>0.75</v>
+        <v>1.55</v>
       </c>
       <c r="F2">
-        <v>-0.8849893868591638</v>
+        <v>-0.4305559626017378</v>
       </c>
       <c r="G2">
-        <v>1.57</v>
+        <v>2.79</v>
       </c>
       <c r="H2">
-        <v>-0.4958946988890265</v>
+        <v>0.6032736115412437</v>
       </c>
       <c r="I2">
-        <v>270.5363952636719</v>
+        <v>177.6059967041016</v>
       </c>
       <c r="J2">
-        <v>269.4896011352539</v>
+        <v>172.4134986877442</v>
       </c>
       <c r="K2">
-        <v>255.9194448852539</v>
+        <v>166.8025991821289</v>
       </c>
       <c r="L2">
-        <v>228.3055249023438</v>
+        <v>160.6740998077393</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
         <v>1.06</v>
       </c>
       <c r="P2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -987,58 +942,58 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>7.777777777777777</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2">
-        <v>175.41</v>
+        <v>110.48</v>
       </c>
       <c r="Y2">
-        <v>275.34</v>
+        <v>184.75</v>
       </c>
       <c r="Z2">
-        <v>63.93</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AA2">
-        <v>12.35</v>
+        <v>10.44</v>
       </c>
       <c r="AB2">
-        <v>12.97</v>
+        <v>764.1799999999999</v>
       </c>
       <c r="AC2">
-        <v>3633.33</v>
+        <v>3285.71</v>
       </c>
       <c r="AD2">
-        <v>33.86</v>
+        <v>10.47</v>
       </c>
       <c r="AE2">
-        <v>626.03</v>
+        <v>80.92</v>
       </c>
       <c r="AF2">
-        <v>461.54</v>
+        <v>-35.78</v>
       </c>
       <c r="AG2">
-        <v>186.67</v>
+        <v>2814.29</v>
       </c>
       <c r="AH2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="AI2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AJ2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="AK2">
-        <v>78.59301029793005</v>
+        <v>93.38338805354631</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,46 +1001,46 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>96.60018132366274</v>
+        <v>94.39361951677223</v>
       </c>
       <c r="C3">
-        <v>2954</v>
+        <v>962</v>
       </c>
       <c r="D3">
-        <v>7.24</v>
+        <v>16.7</v>
       </c>
       <c r="E3">
-        <v>2.48</v>
+        <v>1.22</v>
       </c>
       <c r="F3">
-        <v>0.6282200084183658</v>
+        <v>-0.9511203915232361</v>
       </c>
       <c r="G3">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="H3">
-        <v>0.4229690078759339</v>
+        <v>-1.134972387814882</v>
       </c>
       <c r="I3">
-        <v>7.201251220703125</v>
+        <v>16.4444938659668</v>
       </c>
       <c r="J3">
-        <v>6.912658452987671</v>
+        <v>15.73543386459351</v>
       </c>
       <c r="K3">
-        <v>6.107838516235351</v>
+        <v>14.89983701705933</v>
       </c>
       <c r="L3">
-        <v>4.65891733288765</v>
+        <v>13.05958168506622</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1094,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>12.22222222222222</v>
+        <v>8.888888888888888</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
@@ -1109,46 +1064,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>2.96</v>
+        <v>9.08</v>
       </c>
       <c r="Y3">
-        <v>7.44</v>
+        <v>16.79</v>
       </c>
       <c r="Z3">
-        <v>1.82</v>
+        <v>1.07</v>
       </c>
       <c r="AA3">
-        <v>367.19</v>
+        <v>112000</v>
       </c>
       <c r="AB3">
-        <v>95.83</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="AD3">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="AE3">
-        <v>-35.29</v>
+        <v>5.88</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>-10.53</v>
       </c>
       <c r="AG3">
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="AH3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="AI3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="AK3">
-        <v>70.06319078604423</v>
+        <v>68.33405831903735</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,46 +1111,46 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>96.37352674524026</v>
+        <v>92.9392446633826</v>
       </c>
       <c r="C4">
-        <v>1871</v>
+        <v>98</v>
       </c>
       <c r="D4">
-        <v>101.48</v>
+        <v>23.45</v>
       </c>
       <c r="E4">
-        <v>1.27</v>
+        <v>3.53</v>
       </c>
       <c r="F4">
-        <v>-0.4301518807641838</v>
+        <v>2.69283061092725</v>
       </c>
       <c r="G4">
-        <v>2.59</v>
+        <v>3.09</v>
       </c>
       <c r="H4">
-        <v>0.7213013802022198</v>
+        <v>1.077340702274732</v>
       </c>
       <c r="I4">
-        <v>103.4580001831055</v>
+        <v>23.42600021362305</v>
       </c>
       <c r="J4">
-        <v>103.9795001983643</v>
+        <v>20.90108318328857</v>
       </c>
       <c r="K4">
-        <v>100.1472001647949</v>
+        <v>20.9848331451416</v>
       </c>
       <c r="L4">
-        <v>82.13310026168823</v>
+        <v>19.52198327064514</v>
       </c>
       <c r="M4">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1204,61 +1159,61 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>53.46</v>
+        <v>14.3</v>
       </c>
       <c r="Y4">
-        <v>107.94</v>
+        <v>24.48</v>
       </c>
       <c r="Z4">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="AA4">
-        <v>-239.64</v>
+        <v>296320</v>
       </c>
       <c r="AB4">
-        <v>22.73</v>
+        <v>185.86</v>
       </c>
       <c r="AC4">
-        <v>2750</v>
+        <v>921.1799999999999</v>
       </c>
       <c r="AD4">
-        <v>9.789999999999999</v>
+        <v>19.29</v>
       </c>
       <c r="AE4">
-        <v>381.82</v>
+        <v>170.67</v>
       </c>
       <c r="AF4">
-        <v>-42.11</v>
+        <v>348.95</v>
       </c>
       <c r="AG4">
-        <v>1050</v>
+        <v>-251.55</v>
       </c>
       <c r="AH4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>106</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>116</v>
-      </c>
       <c r="AK4">
-        <v>63.86103836675522</v>
+        <v>66.41911671098168</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,109 +1221,109 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>93.83499546690844</v>
+        <v>98.61599812338729</v>
       </c>
       <c r="C5">
-        <v>2795</v>
+        <v>1580</v>
       </c>
       <c r="D5">
-        <v>41.67</v>
+        <v>134.11</v>
       </c>
       <c r="E5">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="F5">
-        <v>-0.4039112554125503</v>
+        <v>0.6105728952412582</v>
       </c>
       <c r="G5">
-        <v>2.15</v>
+        <v>2.86</v>
       </c>
       <c r="H5">
-        <v>0.1962364049079567</v>
+        <v>0.7138892660457241</v>
       </c>
       <c r="I5">
-        <v>42.12416000366211</v>
+        <v>135.4360015869141</v>
       </c>
       <c r="J5">
-        <v>41.27139625549317</v>
+        <v>128.17200050354</v>
       </c>
       <c r="K5">
-        <v>38.89315475463867</v>
+        <v>124.7924005126953</v>
       </c>
       <c r="L5">
-        <v>30.84768795967102</v>
+        <v>106.5361500930786</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>6.111111111111111</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>20.26</v>
+        <v>54.06</v>
       </c>
       <c r="Y5">
-        <v>43.33</v>
+        <v>140.91</v>
       </c>
       <c r="Z5">
-        <v>1.5</v>
+        <v>4.09</v>
       </c>
       <c r="AA5">
-        <v>7.46</v>
+        <v>-1.22</v>
       </c>
       <c r="AB5">
-        <v>2825</v>
+        <v>129.06</v>
       </c>
       <c r="AC5">
-        <v>241.67</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>5.61</v>
+        <v>7.08</v>
       </c>
       <c r="AE5">
-        <v>-6.82</v>
+        <v>-1</v>
       </c>
       <c r="AF5">
-        <v>266.67</v>
+        <v>25</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>827.27</v>
       </c>
       <c r="AH5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AI5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="AJ5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AK5">
-        <v>56.44254955734991</v>
+        <v>62.72063499360628</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,109 +1331,109 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>91.02447869446962</v>
+        <v>95.80107905231058</v>
       </c>
       <c r="C6">
-        <v>1565</v>
+        <v>1825</v>
       </c>
       <c r="D6">
-        <v>173.82</v>
+        <v>31.05</v>
       </c>
       <c r="E6">
-        <v>1.01</v>
+        <v>2.15</v>
       </c>
       <c r="F6">
-        <v>-0.6575706338116738</v>
+        <v>0.5159248172555313</v>
       </c>
       <c r="G6">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="H6">
-        <v>-0.9732264946110842</v>
+        <v>0.018590866303274</v>
       </c>
       <c r="I6">
-        <v>175.0801239013672</v>
+        <v>30.95799980163574</v>
       </c>
       <c r="J6">
-        <v>174.8827140808106</v>
+        <v>29.65999994277954</v>
       </c>
       <c r="K6">
-        <v>171.7893606567383</v>
+        <v>27.17099990844726</v>
       </c>
       <c r="L6">
-        <v>143.1830255126953</v>
+        <v>27.16399988174438</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>9.444444444444443</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>113.07</v>
+        <v>18.2</v>
       </c>
       <c r="Y6">
-        <v>180.67</v>
+        <v>32.22</v>
       </c>
       <c r="Z6">
-        <v>7.41</v>
+        <v>1.04</v>
       </c>
       <c r="AA6">
-        <v>0.79</v>
+        <v>-0.05</v>
       </c>
       <c r="AB6">
-        <v>339.36</v>
+        <v>60</v>
       </c>
       <c r="AC6">
-        <v>919.51</v>
+        <v>300</v>
       </c>
       <c r="AD6">
-        <v>8.529999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="AE6">
-        <v>30.02</v>
+        <v>333.33</v>
       </c>
       <c r="AF6">
-        <v>404.74</v>
+        <v>-148</v>
       </c>
       <c r="AG6">
-        <v>-357.32</v>
+        <v>257.14</v>
       </c>
       <c r="AH6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>108</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>119</v>
-      </c>
       <c r="AK6">
-        <v>56.20178768135242</v>
+        <v>62.49723315901304</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,109 +1441,112 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>93.51767905711695</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="C7">
-        <v>1589</v>
+        <v>1675</v>
       </c>
       <c r="D7">
-        <v>122.56</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="E7">
-        <v>1.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F7">
-        <v>-0.32518937935765</v>
+        <v>-1.787178413730491</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="H7">
-        <v>-0.4600948142098722</v>
+        <v>-1.751259605768417</v>
       </c>
       <c r="I7">
-        <v>124.0860000610352</v>
+        <v>97.18500366210938</v>
       </c>
       <c r="J7">
-        <v>121.8594997406006</v>
+        <v>93.15356140136718</v>
       </c>
       <c r="K7">
-        <v>117.1847996520996</v>
+        <v>90.87916397094726</v>
       </c>
       <c r="L7">
-        <v>94.33509986877442</v>
+        <v>86.13569568634033</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>1.06</v>
+        <v>1.07</v>
+      </c>
+      <c r="O7" t="s">
+        <v>71</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7">
-        <v>4.444444444444444</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>70.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y7">
-        <v>126.71</v>
+        <v>98.87</v>
       </c>
       <c r="Z7">
-        <v>5.81</v>
+        <v>7.21</v>
       </c>
       <c r="AA7">
-        <v>-2.98</v>
+        <v>409.6</v>
       </c>
       <c r="AB7">
-        <v>155.81</v>
+        <v>54.22</v>
       </c>
       <c r="AC7">
-        <v>333.33</v>
+        <v>522.22</v>
       </c>
       <c r="AD7">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AE7">
-        <v>-58.82</v>
+        <v>124</v>
       </c>
       <c r="AF7">
-        <v>466.67</v>
+        <v>-34.21</v>
       </c>
       <c r="AG7">
-        <v>200</v>
+        <v>322.22</v>
       </c>
       <c r="AH7" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>109</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>120</v>
-      </c>
       <c r="AK7">
-        <v>55.14737779375991</v>
+        <v>57.37782849010313</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1596,49 +1554,49 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>97.37080689029919</v>
+        <v>93.22073657049027</v>
       </c>
       <c r="C8">
-        <v>452</v>
+        <v>1804</v>
       </c>
       <c r="D8">
-        <v>70.47</v>
+        <v>86.98</v>
       </c>
       <c r="E8">
-        <v>1.61</v>
+        <v>3.44</v>
       </c>
       <c r="F8">
-        <v>-0.1327581267790045</v>
+        <v>2.55085849394866</v>
       </c>
       <c r="G8">
-        <v>1.32</v>
+        <v>2.35</v>
       </c>
       <c r="H8">
-        <v>-0.7942270712153124</v>
+        <v>-0.09202478820120645</v>
       </c>
       <c r="I8">
-        <v>68.53138427734375</v>
+        <v>87.89600067138672</v>
       </c>
       <c r="J8">
-        <v>67.08361434936523</v>
+        <v>81.7319995880127</v>
       </c>
       <c r="K8">
-        <v>63.90471778869629</v>
+        <v>76.01940002441407</v>
       </c>
       <c r="L8">
-        <v>53.10882627487182</v>
+        <v>74.59030017852783</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="P8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1647,58 +1605,58 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>35.52</v>
+        <v>57.6</v>
       </c>
       <c r="Y8">
-        <v>71.92</v>
+        <v>90.34</v>
       </c>
       <c r="Z8">
-        <v>22.55</v>
+        <v>1.37</v>
       </c>
       <c r="AA8">
-        <v>6.16</v>
+        <v>5.92</v>
       </c>
       <c r="AB8">
-        <v>6.12</v>
+        <v>302.08</v>
       </c>
       <c r="AC8">
-        <v>247.06</v>
+        <v>657.14</v>
       </c>
       <c r="AD8">
-        <v>5.53</v>
+        <v>3.85</v>
       </c>
       <c r="AE8">
-        <v>68.56999999999999</v>
+        <v>103.85</v>
       </c>
       <c r="AF8">
-        <v>-22.22</v>
+        <v>136.36</v>
       </c>
       <c r="AG8">
-        <v>164.71</v>
+        <v>57.14</v>
       </c>
       <c r="AH8" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>110</v>
       </c>
-      <c r="AJ8" t="s">
-        <v>121</v>
-      </c>
       <c r="AK8">
-        <v>51.59572824533597</v>
+        <v>57.31589991664205</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1706,43 +1664,43 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>91.72710788757932</v>
+        <v>92.47009148486981</v>
       </c>
       <c r="C9">
-        <v>2354</v>
+        <v>1166.5</v>
       </c>
       <c r="D9">
-        <v>111.73</v>
+        <v>134.51</v>
       </c>
       <c r="E9">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="F9">
-        <v>-0.5351143821707177</v>
+        <v>1.004939886848454</v>
       </c>
       <c r="G9">
-        <v>1.2</v>
+        <v>3.48</v>
       </c>
       <c r="H9">
-        <v>-0.9374266099319298</v>
+        <v>1.693627920228268</v>
       </c>
       <c r="I9">
-        <v>112.8080001831055</v>
+        <v>137.2559997558594</v>
       </c>
       <c r="J9">
-        <v>112.7365001678467</v>
+        <v>132.9385002136231</v>
       </c>
       <c r="K9">
-        <v>111.0340000915527</v>
+        <v>127.2374002075195</v>
       </c>
       <c r="L9">
-        <v>89.39675010681152</v>
+        <v>126.6433498382568</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1760,55 +1718,55 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>67.15000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="Y9">
-        <v>117.21</v>
+        <v>164.49</v>
       </c>
       <c r="Z9">
-        <v>1.64</v>
+        <v>3.21</v>
       </c>
       <c r="AA9">
-        <v>6.47</v>
+        <v>-0</v>
       </c>
       <c r="AB9">
-        <v>295.27</v>
+        <v>3446.15</v>
       </c>
       <c r="AC9">
-        <v>395.45</v>
+        <v>360</v>
       </c>
       <c r="AD9">
-        <v>3.73</v>
+        <v>62.82</v>
       </c>
       <c r="AE9">
-        <v>2.83</v>
+        <v>-68.29000000000001</v>
       </c>
       <c r="AF9">
-        <v>103.85</v>
+        <v>143.22</v>
       </c>
       <c r="AG9">
-        <v>136.36</v>
+        <v>437.14</v>
       </c>
       <c r="AH9" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AK9">
-        <v>49.46973911894422</v>
+        <v>56.06612164378372</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1816,43 +1774,43 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>99.79601087941975</v>
+        <v>98.78020173586675</v>
       </c>
       <c r="C10">
-        <v>90</v>
+        <v>314</v>
       </c>
       <c r="D10">
-        <v>30.1</v>
+        <v>35.99</v>
       </c>
       <c r="E10">
-        <v>7.15</v>
+        <v>1.86</v>
       </c>
       <c r="F10">
-        <v>4.713010688155975</v>
+        <v>0.05845910699118471</v>
       </c>
       <c r="G10">
-        <v>4.86</v>
+        <v>3.51</v>
       </c>
       <c r="H10">
-        <v>3.430159320924897</v>
+        <v>1.741034629301616</v>
       </c>
       <c r="I10">
-        <v>24.37999992370606</v>
+        <v>36.20650100708008</v>
       </c>
       <c r="J10">
-        <v>21.16849985122681</v>
+        <v>36.19362545013428</v>
       </c>
       <c r="K10">
-        <v>18.60519994735718</v>
+        <v>32.72155017852783</v>
       </c>
       <c r="L10">
-        <v>10.41564998865127</v>
+        <v>29.64056253433228</v>
       </c>
       <c r="M10">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1873,52 +1831,52 @@
         <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>3.7</v>
+        <v>13.23</v>
       </c>
       <c r="Y10">
-        <v>31.17</v>
+        <v>38.17</v>
       </c>
       <c r="Z10">
-        <v>2.38</v>
+        <v>12.92</v>
       </c>
       <c r="AA10">
-        <v>-11.34</v>
+        <v>-134.43</v>
       </c>
       <c r="AB10">
-        <v>143.48</v>
+        <v>173.13</v>
       </c>
       <c r="AC10">
-        <v>400</v>
+        <v>630</v>
       </c>
       <c r="AD10">
-        <v>9.050000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE10">
-        <v>200</v>
+        <v>55.88</v>
       </c>
       <c r="AF10">
-        <v>200</v>
+        <v>221.43</v>
       </c>
       <c r="AG10">
-        <v>133.33</v>
+        <v>-180</v>
       </c>
       <c r="AH10" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="AJ10" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="AK10">
-        <v>49.28493662829513</v>
+        <v>55.80312860613128</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1926,49 +1884,52 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>92.11242067089755</v>
+        <v>92.09476894205957</v>
       </c>
       <c r="C11">
-        <v>1008</v>
+        <v>2639</v>
       </c>
       <c r="D11">
-        <v>91.33</v>
+        <v>138.76</v>
       </c>
       <c r="E11">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="F11">
-        <v>0.3833075051364537</v>
+        <v>-1.108867188166114</v>
       </c>
       <c r="G11">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="H11">
-        <v>-0.5197612886751295</v>
+        <v>-1.593237242190588</v>
       </c>
       <c r="I11">
-        <v>88.839111328125</v>
+        <v>136.2988647460938</v>
       </c>
       <c r="J11">
-        <v>86.1628402709961</v>
+        <v>128.3129222869873</v>
       </c>
       <c r="K11">
-        <v>81.92419311523437</v>
+        <v>121.2815382385254</v>
       </c>
       <c r="L11">
-        <v>67.59650373458862</v>
+        <v>110.8638854980469</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
-        <v>1.08</v>
+        <v>1.12</v>
+      </c>
+      <c r="O11" t="s">
+        <v>71</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1977,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>1.111111111111111</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -1989,46 +1950,46 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>47.93</v>
+        <v>95.19</v>
       </c>
       <c r="Y11">
-        <v>96.03</v>
+        <v>139.14</v>
       </c>
       <c r="Z11">
-        <v>4.67</v>
+        <v>5.85</v>
       </c>
       <c r="AA11">
-        <v>23.49</v>
+        <v>6.5</v>
       </c>
       <c r="AB11">
-        <v>1077.19</v>
+        <v>6.18</v>
       </c>
       <c r="AC11">
-        <v>237.5</v>
+        <v>155.88</v>
       </c>
       <c r="AD11">
-        <v>22.11</v>
+        <v>8.73</v>
       </c>
       <c r="AE11">
-        <v>-49.3</v>
+        <v>0.58</v>
       </c>
       <c r="AF11">
-        <v>597.22</v>
+        <v>21.83</v>
       </c>
       <c r="AG11">
-        <v>45.45</v>
+        <v>108.82</v>
       </c>
       <c r="AH11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="AK11">
-        <v>47.7539367763011</v>
+        <v>55.55502354414558</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2036,46 +1997,46 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>90.59383499546691</v>
+        <v>96.5986394557823</v>
       </c>
       <c r="C12">
-        <v>762</v>
+        <v>692</v>
       </c>
       <c r="D12">
-        <v>171.13</v>
+        <v>9.07</v>
       </c>
       <c r="E12">
-        <v>0.89</v>
+        <v>1.46</v>
       </c>
       <c r="F12">
-        <v>-0.7625331352182076</v>
+        <v>-0.5725280795803284</v>
       </c>
       <c r="G12">
-        <v>1.09</v>
+        <v>2.03</v>
       </c>
       <c r="H12">
-        <v>-1.068692853755496</v>
+        <v>-0.5976963516502616</v>
       </c>
       <c r="I12">
-        <v>175.8189666748047</v>
+        <v>9.016581535339355</v>
       </c>
       <c r="J12">
-        <v>175.7913429260254</v>
+        <v>8.349564719200135</v>
       </c>
       <c r="K12">
-        <v>168.8892327880859</v>
+        <v>7.728608884811401</v>
       </c>
       <c r="L12">
-        <v>145.6264278411865</v>
+        <v>7.243961091041565</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12">
         <v>2</v>
@@ -2084,61 +2045,61 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>2.222222222222222</v>
+        <v>5</v>
       </c>
       <c r="U12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>113.13</v>
+        <v>4.79</v>
       </c>
       <c r="Y12">
-        <v>182.34</v>
+        <v>9.17</v>
       </c>
       <c r="Z12">
-        <v>56.94</v>
+        <v>1.58</v>
       </c>
       <c r="AA12">
-        <v>8.82</v>
+        <v>-35.49</v>
       </c>
       <c r="AB12">
-        <v>37.19</v>
+        <v>104.44</v>
       </c>
       <c r="AC12">
-        <v>200</v>
+        <v>213.33</v>
       </c>
       <c r="AD12">
-        <v>12.06</v>
+        <v>5.03</v>
       </c>
       <c r="AE12">
-        <v>-3.16</v>
+        <v>193.75</v>
       </c>
       <c r="AF12">
-        <v>16.18</v>
+        <v>14.29</v>
       </c>
       <c r="AG12">
-        <v>166.67</v>
+        <v>-6.67</v>
       </c>
       <c r="AH12" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="AK12">
-        <v>46.9353245203839</v>
+        <v>52.54396597761073</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2146,49 +2107,49 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>97.73345421577517</v>
+        <v>92.7046680741262</v>
       </c>
       <c r="C13">
-        <v>912</v>
+        <v>1672</v>
       </c>
       <c r="D13">
-        <v>29.53</v>
+        <v>27.85</v>
       </c>
       <c r="E13">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="F13">
-        <v>0.2870918788471307</v>
+        <v>0.2950793019555015</v>
       </c>
       <c r="G13">
-        <v>3.33</v>
+        <v>2.1</v>
       </c>
       <c r="H13">
-        <v>1.604365202288026</v>
+        <v>-0.4870806971457805</v>
       </c>
       <c r="I13">
-        <v>29.26599998474121</v>
+        <v>28.05671577453613</v>
       </c>
       <c r="J13">
-        <v>28.34900007247925</v>
+        <v>26.35616483688354</v>
       </c>
       <c r="K13">
-        <v>26.99800010681152</v>
+        <v>25.26356117248535</v>
       </c>
       <c r="L13">
-        <v>18.71527501583099</v>
+        <v>23.7935027217865</v>
       </c>
       <c r="M13">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2197,58 +2158,58 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="b">
         <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>10.41</v>
+        <v>17.48</v>
       </c>
       <c r="Y13">
-        <v>30.73</v>
+        <v>28.5</v>
       </c>
       <c r="Z13">
-        <v>1.8</v>
+        <v>12.41</v>
       </c>
       <c r="AA13">
-        <v>-0.96</v>
+        <v>-8197.530000000001</v>
       </c>
       <c r="AB13">
-        <v>111.84</v>
+        <v>8400</v>
       </c>
       <c r="AC13">
-        <v>238.89</v>
+        <v>158.88</v>
       </c>
       <c r="AD13">
-        <v>11.91</v>
+        <v>41.04</v>
       </c>
       <c r="AE13">
-        <v>92.31</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AF13">
-        <v>218.18</v>
+        <v>-15.94</v>
       </c>
       <c r="AG13">
-        <v>38.89</v>
+        <v>164.49</v>
       </c>
       <c r="AH13" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="AK13">
-        <v>45.11663138887651</v>
+        <v>51.54333259309116</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2256,49 +2217,49 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>93.81233000906619</v>
+        <v>95.91836734693877</v>
       </c>
       <c r="C14">
-        <v>1815</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>193.74</v>
+        <v>15.87</v>
       </c>
       <c r="E14">
-        <v>1.21</v>
+        <v>1.95</v>
       </c>
       <c r="F14">
-        <v>-0.4826331314674507</v>
+        <v>0.2004312239697749</v>
       </c>
       <c r="G14">
-        <v>1.61</v>
+        <v>2.66</v>
       </c>
       <c r="H14">
-        <v>-0.4481615193168207</v>
+        <v>0.3978445388900654</v>
       </c>
       <c r="I14">
-        <v>196.9440002441406</v>
+        <v>16.06359958648682</v>
       </c>
       <c r="J14">
-        <v>193.5805000305176</v>
+        <v>14.9654999256134</v>
       </c>
       <c r="K14">
-        <v>180.9916000366211</v>
+        <v>14.53919996261597</v>
       </c>
       <c r="L14">
-        <v>154.1531998825073</v>
+        <v>14.42963998317719</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P14">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2307,58 +2268,58 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>104.77</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Y14">
-        <v>201</v>
+        <v>18.87</v>
       </c>
       <c r="Z14">
-        <v>9.68</v>
+        <v>12.27</v>
       </c>
       <c r="AA14">
-        <v>28.67</v>
+        <v>1933.59</v>
       </c>
       <c r="AB14">
-        <v>42.07</v>
+        <v>360.47</v>
       </c>
       <c r="AC14">
-        <v>19.15</v>
+        <v>336</v>
       </c>
       <c r="AD14">
-        <v>4.54</v>
+        <v>18.34</v>
       </c>
       <c r="AE14">
-        <v>0.9</v>
+        <v>211.43</v>
       </c>
       <c r="AF14">
-        <v>-9.02</v>
+        <v>20.69</v>
       </c>
       <c r="AG14">
-        <v>29.79</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AJ14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AK14">
-        <v>43.29032302078185</v>
+        <v>50.94041038888952</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2366,109 +2327,109 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>99.32003626473255</v>
+        <v>90.38235984048792</v>
       </c>
       <c r="C15">
-        <v>4199.5</v>
+        <v>178</v>
       </c>
       <c r="D15">
-        <v>18.87</v>
+        <v>29.19</v>
       </c>
       <c r="E15">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="F15">
-        <v>0.2258637530266528</v>
+        <v>1.225785402148484</v>
       </c>
       <c r="G15">
-        <v>2.72</v>
+        <v>2.43</v>
       </c>
       <c r="H15">
-        <v>0.8764342138118889</v>
+        <v>0.03439310266105733</v>
       </c>
       <c r="I15">
-        <v>18.94059944152832</v>
+        <v>26.79396018981934</v>
       </c>
       <c r="J15">
-        <v>18.43789987564087</v>
+        <v>24.745729637146</v>
       </c>
       <c r="K15">
-        <v>16.02588001251221</v>
+        <v>23.72328491210937</v>
       </c>
       <c r="L15">
-        <v>11.44149000644684</v>
+        <v>23.30280796051025</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="U15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>5.84</v>
+        <v>20.32</v>
       </c>
       <c r="Y15">
-        <v>19.2</v>
+        <v>29.33</v>
       </c>
       <c r="Z15">
-        <v>1.05</v>
+        <v>3.54</v>
       </c>
       <c r="AA15">
-        <v>0.09</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="AB15">
-        <v>162.5</v>
+        <v>375</v>
       </c>
       <c r="AC15">
-        <v>181.82</v>
+        <v>161.54</v>
       </c>
       <c r="AD15">
-        <v>12.87</v>
+        <v>5.46</v>
       </c>
       <c r="AE15">
-        <v>38.46</v>
+        <v>126.67</v>
       </c>
       <c r="AF15">
-        <v>116.67</v>
+        <v>7.14</v>
       </c>
       <c r="AG15">
-        <v>127.27</v>
+        <v>7.69</v>
       </c>
       <c r="AH15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AJ15" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="AK15">
-        <v>43.10475909932633</v>
+        <v>48.45705791674369</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2476,46 +2437,46 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>96.55485040797825</v>
+        <v>96.71592775041051</v>
       </c>
       <c r="C16">
-        <v>1985.5</v>
+        <v>1933</v>
       </c>
       <c r="D16">
-        <v>359.81</v>
+        <v>45.21</v>
       </c>
       <c r="E16">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="F16">
-        <v>-0.4214050056469726</v>
+        <v>-0.5567533999160406</v>
       </c>
       <c r="G16">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="H16">
-        <v>-0.4242949295307181</v>
+        <v>-0.04461807912785789</v>
       </c>
       <c r="I16">
-        <v>351.9940063476562</v>
+        <v>44.98399963378906</v>
       </c>
       <c r="J16">
-        <v>343.9165008544922</v>
+        <v>44.05574970245361</v>
       </c>
       <c r="K16">
-        <v>320.602001953125</v>
+        <v>42.50389991760254</v>
       </c>
       <c r="L16">
-        <v>252.8707006072998</v>
+        <v>42.27484987258911</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2527,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>3.888888888888888</v>
+        <v>0</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
@@ -2539,46 +2500,46 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>170.26</v>
+        <v>26.16</v>
       </c>
       <c r="Y16">
-        <v>371.81</v>
+        <v>50.34</v>
       </c>
       <c r="Z16">
-        <v>9.51</v>
+        <v>1.76</v>
       </c>
       <c r="AA16">
-        <v>9.01</v>
+        <v>2320</v>
       </c>
       <c r="AB16">
-        <v>2.44</v>
+        <v>625</v>
       </c>
       <c r="AC16">
-        <v>95.58</v>
+        <v>217.95</v>
       </c>
       <c r="AD16">
-        <v>23.91</v>
+        <v>2.6</v>
       </c>
       <c r="AE16">
-        <v>92.17</v>
+        <v>43.75</v>
       </c>
       <c r="AF16">
-        <v>-16.67</v>
+        <v>68.42</v>
       </c>
       <c r="AG16">
-        <v>22.12</v>
+        <v>148.72</v>
       </c>
       <c r="AH16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI16" t="s">
         <v>94</v>
       </c>
-      <c r="AI16" t="s">
-        <v>106</v>
-      </c>
       <c r="AJ16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AK16">
-        <v>42.92876063382775</v>
+        <v>47.68955401202449</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2586,43 +2547,43 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>91.70444242973707</v>
+        <v>95.12080694346704</v>
       </c>
       <c r="C17">
-        <v>860</v>
+        <v>2585</v>
       </c>
       <c r="D17">
-        <v>32.76</v>
+        <v>61.29</v>
       </c>
       <c r="E17">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="F17">
-        <v>0.4270418807225093</v>
+        <v>0.7052209732269853</v>
       </c>
       <c r="G17">
-        <v>3.18</v>
+        <v>2.14</v>
       </c>
       <c r="H17">
-        <v>1.425365778892255</v>
+        <v>-0.4238717517146485</v>
       </c>
       <c r="I17">
-        <v>32.3879997253418</v>
+        <v>60.30933685302735</v>
       </c>
       <c r="J17">
-        <v>33.3855001449585</v>
+        <v>57.22422180175781</v>
       </c>
       <c r="K17">
-        <v>32.25559997558594</v>
+        <v>56.21664924621582</v>
       </c>
       <c r="L17">
-        <v>26.93674997806549</v>
+        <v>52.81013185501099</v>
       </c>
       <c r="M17">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -2631,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -2646,49 +2607,49 @@
         <v>1</v>
       </c>
       <c r="W17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>15.01</v>
+        <v>36.63</v>
       </c>
       <c r="Y17">
-        <v>39.59</v>
+        <v>61.62</v>
       </c>
       <c r="Z17">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AA17">
-        <v>310.09</v>
+        <v>1.56</v>
       </c>
       <c r="AB17">
-        <v>2.76</v>
+        <v>9.66</v>
       </c>
       <c r="AC17">
-        <v>112.5</v>
+        <v>361.54</v>
       </c>
       <c r="AD17">
-        <v>3.53</v>
+        <v>4.15</v>
       </c>
       <c r="AE17">
-        <v>6.25</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="AF17">
-        <v>-52.24</v>
+        <v>-31.37</v>
       </c>
       <c r="AG17">
-        <v>318.75</v>
+        <v>292.31</v>
       </c>
       <c r="AH17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="AJ17" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="AK17">
-        <v>42.42459618818444</v>
+        <v>44.74454885352728</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2696,43 +2657,43 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>96.05621033544878</v>
+        <v>92.11822660098522</v>
       </c>
       <c r="C18">
-        <v>304</v>
+        <v>486</v>
       </c>
       <c r="D18">
-        <v>45.1</v>
+        <v>52.17</v>
       </c>
       <c r="E18">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
       <c r="F18">
-        <v>0.7681700102937444</v>
+        <v>0.4843754579269556</v>
       </c>
       <c r="G18">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H18">
-        <v>0.9241673933840941</v>
+        <v>0.2398221753122356</v>
       </c>
       <c r="I18">
-        <v>45.71999893188477</v>
+        <v>52.12577438354492</v>
       </c>
       <c r="J18">
-        <v>44.64649963378906</v>
+        <v>50.9550443649292</v>
       </c>
       <c r="K18">
-        <v>39.17260002136231</v>
+        <v>51.52498123168945</v>
       </c>
       <c r="L18">
-        <v>28.76334998130798</v>
+        <v>48.06716646194458</v>
       </c>
       <c r="M18">
         <v>1.02</v>
       </c>
       <c r="N18">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2741,64 +2702,64 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>9.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="U18" t="b">
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="b">
         <v>0</v>
       </c>
       <c r="X18">
-        <v>17.02</v>
+        <v>32.25</v>
       </c>
       <c r="Y18">
-        <v>48.88</v>
+        <v>61.36</v>
       </c>
       <c r="Z18">
-        <v>9.57</v>
+        <v>6.4</v>
       </c>
       <c r="AA18">
-        <v>0.48</v>
+        <v>1.22</v>
       </c>
       <c r="AB18">
-        <v>143.54</v>
+        <v>241.67</v>
       </c>
       <c r="AC18">
-        <v>22.19</v>
+        <v>183.33</v>
       </c>
       <c r="AD18">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="AE18">
-        <v>10.7</v>
+        <v>117.39</v>
       </c>
       <c r="AF18">
-        <v>23.56</v>
+        <v>475</v>
       </c>
       <c r="AG18">
-        <v>-10.67</v>
+        <v>106.67</v>
       </c>
       <c r="AH18" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AK18">
-        <v>42.14125760712199</v>
+        <v>44.09743911461402</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2806,46 +2767,46 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>96.82683590208522</v>
+        <v>98.56908280553601</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>926</v>
       </c>
       <c r="D19">
-        <v>15.81</v>
+        <v>77.52</v>
       </c>
       <c r="E19">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="F19">
-        <v>-0.03654250048968188</v>
+        <v>0.1057831459840479</v>
       </c>
       <c r="G19">
-        <v>1.73</v>
+        <v>2.94</v>
       </c>
       <c r="H19">
-        <v>-0.3049619806002036</v>
+        <v>0.8403071569079879</v>
       </c>
       <c r="I19">
-        <v>15.92039985656738</v>
+        <v>76.06972961425781</v>
       </c>
       <c r="J19">
-        <v>15.27028994560242</v>
+        <v>75.71836051940917</v>
       </c>
       <c r="K19">
-        <v>14.61010000228882</v>
+        <v>71.1615151977539</v>
       </c>
       <c r="L19">
-        <v>12.13014401197433</v>
+        <v>67.93195436477662</v>
       </c>
       <c r="M19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -2857,58 +2818,58 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>1.111111111111111</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="U19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="b">
         <v>1</v>
       </c>
       <c r="W19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>7.66</v>
+        <v>30.75</v>
       </c>
       <c r="Y19">
-        <v>16.24</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="Z19">
-        <v>20.74</v>
+        <v>6.15</v>
       </c>
       <c r="AA19">
-        <v>36.43</v>
+        <v>-5224.49</v>
       </c>
       <c r="AB19">
-        <v>20.67</v>
+        <v>106.45</v>
       </c>
       <c r="AC19">
-        <v>139.42</v>
+        <v>178.95</v>
       </c>
       <c r="AD19">
-        <v>5.92</v>
+        <v>13.03</v>
       </c>
       <c r="AE19">
-        <v>3.14</v>
+        <v>23.26</v>
       </c>
       <c r="AF19">
-        <v>174.14</v>
+        <v>230.77</v>
       </c>
       <c r="AG19">
-        <v>-15.33</v>
+        <v>-31.58</v>
       </c>
       <c r="AH19" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AJ19" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="AK19">
-        <v>42.05620866938408</v>
+        <v>43.2062011314501</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2916,43 +2877,43 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>96.87216681776972</v>
+        <v>95.6368754398311</v>
       </c>
       <c r="C20">
-        <v>1554</v>
+        <v>1218</v>
       </c>
       <c r="D20">
-        <v>626.45</v>
+        <v>137.8</v>
       </c>
       <c r="E20">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="F20">
-        <v>0.0596731257996409</v>
+        <v>-0.5883027592446162</v>
       </c>
       <c r="G20">
-        <v>1.99</v>
+        <v>3.27</v>
       </c>
       <c r="H20">
-        <v>0.005303686619133742</v>
+        <v>1.361780956714826</v>
       </c>
       <c r="I20">
-        <v>637.9500122070312</v>
+        <v>137.9740020751953</v>
       </c>
       <c r="J20">
-        <v>639.0434997558593</v>
+        <v>135.3825012207031</v>
       </c>
       <c r="K20">
-        <v>618.5007995605469</v>
+        <v>129.1932005310059</v>
       </c>
       <c r="L20">
-        <v>455.683699798584</v>
+        <v>119.8574500274658</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N20">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2970,55 +2931,55 @@
         <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>257.52</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="Y20">
-        <v>672.55</v>
+        <v>154.06</v>
       </c>
       <c r="Z20">
-        <v>23.35</v>
+        <v>10.1</v>
       </c>
       <c r="AA20">
-        <v>-1.42</v>
+        <v>24.96</v>
       </c>
       <c r="AB20">
-        <v>69.92</v>
+        <v>136.76</v>
       </c>
       <c r="AC20">
-        <v>152</v>
+        <v>169.25</v>
       </c>
       <c r="AD20">
-        <v>0.54</v>
+        <v>12.62</v>
       </c>
       <c r="AE20">
-        <v>360</v>
+        <v>-2.13</v>
       </c>
       <c r="AF20">
-        <v>78.26000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="AG20">
-        <v>8</v>
+        <v>138.49</v>
       </c>
       <c r="AH20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="AJ20" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="AK20">
-        <v>41.37278275915087</v>
+        <v>42.18600406180081</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3026,49 +2987,49 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>91.06980961015412</v>
+        <v>91.93056532958011</v>
       </c>
       <c r="C21">
-        <v>1064</v>
+        <v>65</v>
       </c>
       <c r="D21">
-        <v>12.06</v>
+        <v>61.23</v>
       </c>
       <c r="E21">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="F21">
-        <v>-0.4738862563502396</v>
+        <v>-0.8880216728660848</v>
       </c>
       <c r="G21">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H21">
-        <v>-0.7942270712153124</v>
+        <v>-1.609039478548371</v>
       </c>
       <c r="I21">
-        <v>12.21737041473389</v>
+        <v>61.3208610534668</v>
       </c>
       <c r="J21">
-        <v>12.23584747314453</v>
+        <v>59.75189437866211</v>
       </c>
       <c r="K21">
-        <v>11.91643497467041</v>
+        <v>60.15857162475586</v>
       </c>
       <c r="L21">
-        <v>9.876379516124725</v>
+        <v>54.04446710586548</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -3077,58 +3038,58 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>6.57</v>
+        <v>41.08</v>
       </c>
       <c r="Y21">
-        <v>12.62</v>
+        <v>63.47</v>
       </c>
       <c r="Z21">
-        <v>1.39</v>
+        <v>163.16</v>
       </c>
       <c r="AA21">
-        <v>-4000</v>
+        <v>10.92</v>
       </c>
       <c r="AB21">
-        <v>176.05</v>
+        <v>103.48</v>
       </c>
       <c r="AC21">
-        <v>112.9</v>
+        <v>159.26</v>
       </c>
       <c r="AD21">
-        <v>2.79</v>
+        <v>6.61</v>
       </c>
       <c r="AE21">
-        <v>-69.23</v>
+        <v>-4.11</v>
       </c>
       <c r="AF21">
-        <v>-75.93000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="AG21">
-        <v>274.19</v>
+        <v>137.04</v>
       </c>
       <c r="AH21" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="AJ21" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="AK21">
-        <v>41.20180202141095</v>
+        <v>41.03492852894748</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3136,46 +3097,46 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>98.00543970988214</v>
+        <v>97.04433497536947</v>
       </c>
       <c r="C22">
-        <v>1243</v>
+        <v>1352</v>
       </c>
       <c r="D22">
-        <v>201.38</v>
+        <v>27.64</v>
       </c>
       <c r="E22">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
       <c r="F22">
-        <v>-0.386417505178128</v>
+        <v>0.3108539816197897</v>
       </c>
       <c r="G22">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="H22">
-        <v>0.3633025334106769</v>
+        <v>-0.2184426790634702</v>
       </c>
       <c r="I22">
-        <v>204.6365936279297</v>
+        <v>27.40960311889648</v>
       </c>
       <c r="J22">
-        <v>197.029328918457</v>
+        <v>27.00992965698242</v>
       </c>
       <c r="K22">
-        <v>176.9410943603516</v>
+        <v>26.79641693115234</v>
       </c>
       <c r="L22">
-        <v>134.239444770813</v>
+        <v>23.64803307533264</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3184,61 +3145,61 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.222222222222222</v>
+        <v>0</v>
       </c>
       <c r="U22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="b">
         <v>0</v>
       </c>
       <c r="X22">
-        <v>75.84</v>
+        <v>14.3</v>
       </c>
       <c r="Y22">
-        <v>210.28</v>
+        <v>29.19</v>
       </c>
       <c r="Z22">
-        <v>8.52</v>
+        <v>1.74</v>
       </c>
       <c r="AA22">
-        <v>12.42</v>
+        <v>44.55</v>
       </c>
       <c r="AB22">
-        <v>35.16</v>
+        <v>3.09</v>
       </c>
       <c r="AC22">
-        <v>91.67</v>
+        <v>300</v>
       </c>
       <c r="AD22">
-        <v>5.78</v>
+        <v>10.74</v>
       </c>
       <c r="AE22">
-        <v>39.39</v>
+        <v>14.29</v>
       </c>
       <c r="AF22">
-        <v>65</v>
+        <v>-12.5</v>
       </c>
       <c r="AG22">
-        <v>-16.67</v>
+        <v>300</v>
       </c>
       <c r="AH22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="AJ22" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="AK22">
-        <v>40.77559687502635</v>
+        <v>40.99248506460243</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3246,43 +3207,43 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>91.97642792384406</v>
+        <v>96.31714754867464</v>
       </c>
       <c r="C23">
-        <v>1722</v>
+        <v>236</v>
       </c>
       <c r="D23">
-        <v>20.88</v>
+        <v>55.76</v>
       </c>
       <c r="E23">
-        <v>0.75</v>
+        <v>2.27</v>
       </c>
       <c r="F23">
-        <v>-0.8849893868591638</v>
+        <v>0.7052209732269853</v>
       </c>
       <c r="G23">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
       <c r="H23">
-        <v>-1.367025226081781</v>
+        <v>1.251165302210345</v>
       </c>
       <c r="I23">
-        <v>21.04116325378418</v>
+        <v>54.73600006103516</v>
       </c>
       <c r="J23">
-        <v>20.69325933456421</v>
+        <v>50.33400039672851</v>
       </c>
       <c r="K23">
-        <v>19.79182365417481</v>
+        <v>44.68933303833008</v>
       </c>
       <c r="L23">
-        <v>18.05565248012543</v>
+        <v>43.72297790527344</v>
       </c>
       <c r="M23">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N23">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3300,55 +3261,55 @@
         <v>0</v>
       </c>
       <c r="U23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" t="b">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>14.05</v>
+        <v>31.47</v>
       </c>
       <c r="Y23">
-        <v>21.24</v>
+        <v>60.91</v>
       </c>
       <c r="Z23">
-        <v>1.58</v>
+        <v>16.73</v>
       </c>
       <c r="AA23">
-        <v>1.25</v>
+        <v>10.08</v>
       </c>
       <c r="AB23">
-        <v>155.43</v>
+        <v>60.81</v>
       </c>
       <c r="AC23">
-        <v>83.05</v>
+        <v>166.28</v>
       </c>
       <c r="AD23">
-        <v>13.47</v>
+        <v>6.12</v>
       </c>
       <c r="AE23">
-        <v>178.83</v>
+        <v>30.86</v>
       </c>
       <c r="AF23">
-        <v>-221.24</v>
+        <v>-32.95</v>
       </c>
       <c r="AG23">
-        <v>91.53</v>
+        <v>203.49</v>
       </c>
       <c r="AH23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="AJ23" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="AK23">
-        <v>36.92658550513797</v>
+        <v>40.43317341457575</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3356,52 +3317,49 @@
         <v>59</v>
       </c>
       <c r="B24">
-        <v>91.93109700815957</v>
+        <v>90.40581749941356</v>
       </c>
       <c r="C24">
-        <v>1970</v>
+        <v>393</v>
       </c>
       <c r="D24">
-        <v>64.39</v>
+        <v>12.4</v>
       </c>
       <c r="E24">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="F24">
-        <v>0.1034075013856965</v>
+        <v>0.7209956528912728</v>
       </c>
       <c r="G24">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="H24">
-        <v>-0.5674944682473353</v>
+        <v>-0.2026404427056876</v>
       </c>
       <c r="I24">
-        <v>64.80264892578126</v>
+        <v>12.35672340393066</v>
       </c>
       <c r="J24">
-        <v>60.30685539245606</v>
+        <v>11.90563702583313</v>
       </c>
       <c r="K24">
-        <v>56.88309494018554</v>
+        <v>11.54945806503296</v>
       </c>
       <c r="L24">
-        <v>51.7613667678833</v>
+        <v>10.9181679391861</v>
       </c>
       <c r="M24">
+        <v>1.04</v>
+      </c>
+      <c r="N24">
         <v>1.07</v>
       </c>
-      <c r="N24">
-        <v>1.14</v>
-      </c>
-      <c r="O24" t="s">
-        <v>82</v>
-      </c>
       <c r="P24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -3410,58 +3368,58 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="b">
         <v>1</v>
       </c>
       <c r="W24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>41.69</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Y24">
-        <v>66.39</v>
+        <v>12.75</v>
       </c>
       <c r="Z24">
-        <v>2.98</v>
+        <v>4.39</v>
       </c>
       <c r="AA24">
-        <v>32.35</v>
+        <v>-2.55</v>
       </c>
       <c r="AB24">
-        <v>14.51</v>
+        <v>85.28</v>
       </c>
       <c r="AC24">
-        <v>21.21</v>
+        <v>146.21</v>
       </c>
       <c r="AD24">
-        <v>6.11</v>
+        <v>0.58</v>
       </c>
       <c r="AE24">
-        <v>-6.98</v>
+        <v>136.39</v>
       </c>
       <c r="AF24">
-        <v>43.33</v>
+        <v>-232.94</v>
       </c>
       <c r="AG24">
-        <v>-9.09</v>
+        <v>195.52</v>
       </c>
       <c r="AH24" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="AK24">
-        <v>36.39784236969835</v>
+        <v>39.80552999297435</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3469,46 +3427,49 @@
         <v>60</v>
       </c>
       <c r="B25">
-        <v>90.45784224841343</v>
+        <v>95.68379075768239</v>
       </c>
       <c r="C25">
-        <v>2271</v>
+        <v>181</v>
       </c>
       <c r="D25">
-        <v>59.46</v>
+        <v>14.26</v>
       </c>
       <c r="E25">
-        <v>2.67</v>
+        <v>1.06</v>
       </c>
       <c r="F25">
-        <v>0.7944106356453777</v>
+        <v>-1.203515266151841</v>
       </c>
       <c r="G25">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="H25">
-        <v>-0.0304961980600206</v>
+        <v>-1.134972387814882</v>
       </c>
       <c r="I25">
-        <v>57.0620002746582</v>
+        <v>14.09134101867676</v>
       </c>
       <c r="J25">
-        <v>54.34700050354004</v>
+        <v>13.26246118545532</v>
       </c>
       <c r="K25">
-        <v>51.95360046386719</v>
+        <v>12.75594963073731</v>
       </c>
       <c r="L25">
-        <v>50.2432501411438</v>
+        <v>11.49456377506256</v>
       </c>
       <c r="M25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
         <v>1.1</v>
       </c>
+      <c r="O25" t="s">
+        <v>71</v>
+      </c>
       <c r="P25">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -3520,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
@@ -3529,49 +3490,49 @@
         <v>1</v>
       </c>
       <c r="W25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>44.6</v>
+        <v>7.92</v>
       </c>
       <c r="Y25">
-        <v>64.39</v>
+        <v>14.27</v>
       </c>
       <c r="Z25">
-        <v>1.13</v>
+        <v>7.63</v>
       </c>
       <c r="AA25">
-        <v>1.05</v>
+        <v>-47.59</v>
       </c>
       <c r="AB25">
-        <v>265.71</v>
+        <v>87.5</v>
       </c>
       <c r="AC25">
-        <v>23.08</v>
+        <v>107.39</v>
       </c>
       <c r="AD25">
-        <v>1.86</v>
+        <v>3.36</v>
       </c>
       <c r="AE25">
-        <v>220</v>
+        <v>-65.91</v>
       </c>
       <c r="AF25">
-        <v>7.14</v>
+        <v>-57.69</v>
       </c>
       <c r="AG25">
-        <v>-64.09999999999999</v>
+        <v>151.23</v>
       </c>
       <c r="AH25" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AI25" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AJ25" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="AK25">
-        <v>35.40195376804186</v>
+        <v>39.63830286595094</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3579,58 +3540,58 @@
         <v>61</v>
       </c>
       <c r="B26">
-        <v>93.65367180417044</v>
+        <v>97.4900304949566</v>
       </c>
       <c r="C26">
-        <v>713</v>
+        <v>652</v>
       </c>
       <c r="D26">
-        <v>63.24</v>
+        <v>112.94</v>
       </c>
       <c r="E26">
-        <v>1.26</v>
+        <v>2.17</v>
       </c>
       <c r="F26">
-        <v>-0.4388987558813949</v>
+        <v>0.5474741765841069</v>
       </c>
       <c r="G26">
-        <v>0.99</v>
+        <v>3.25</v>
       </c>
       <c r="H26">
-        <v>-1.18802580268601</v>
+        <v>1.33017648399926</v>
       </c>
       <c r="I26">
-        <v>63.84614715576172</v>
+        <v>114.6600006103516</v>
       </c>
       <c r="J26">
-        <v>62.64514598846436</v>
+        <v>106.541499710083</v>
       </c>
       <c r="K26">
-        <v>60.71607955932618</v>
+        <v>96.82179977416992</v>
       </c>
       <c r="L26">
-        <v>51.17540538787842</v>
+        <v>89.26889995574952</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="P26">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7.777777777777777</v>
       </c>
       <c r="U26" t="b">
         <v>0</v>
@@ -3642,46 +3603,46 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>39.35</v>
+        <v>52.17</v>
       </c>
       <c r="Y26">
-        <v>65.95999999999999</v>
+        <v>117.28</v>
       </c>
       <c r="Z26">
-        <v>8.57</v>
+        <v>14.25</v>
       </c>
       <c r="AA26">
-        <v>14.8</v>
+        <v>690</v>
       </c>
       <c r="AB26">
-        <v>3.39</v>
+        <v>6.15</v>
       </c>
       <c r="AC26">
-        <v>27.69</v>
+        <v>57.14</v>
       </c>
       <c r="AD26">
-        <v>15.68</v>
+        <v>5.63</v>
       </c>
       <c r="AE26">
-        <v>27.69</v>
+        <v>25.71</v>
       </c>
       <c r="AF26">
-        <v>-29.35</v>
+        <v>12.9</v>
       </c>
       <c r="AG26">
-        <v>41.54</v>
+        <v>10.71</v>
       </c>
       <c r="AH26" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="AK26">
-        <v>35.21651596386831</v>
+        <v>38.91141564166274</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3689,49 +3650,52 @@
         <v>62</v>
       </c>
       <c r="B27">
-        <v>98.43608340888485</v>
+        <v>93.83063570255689</v>
       </c>
       <c r="C27">
-        <v>1142</v>
+        <v>689</v>
       </c>
       <c r="D27">
-        <v>138.37</v>
+        <v>49.26</v>
       </c>
       <c r="E27">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="F27">
-        <v>0.2521043783782861</v>
+        <v>-0.761824235551782</v>
       </c>
       <c r="G27">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="H27">
-        <v>0.5661685465925512</v>
+        <v>-1.134972387814882</v>
       </c>
       <c r="I27">
-        <v>141.3220001220703</v>
+        <v>48.14352798461914</v>
       </c>
       <c r="J27">
-        <v>138.2160007476807</v>
+        <v>44.39835376739502</v>
       </c>
       <c r="K27">
-        <v>133.0888008117676</v>
+        <v>43.82404304504394</v>
       </c>
       <c r="L27">
-        <v>103.6639500808716</v>
+        <v>42.84669921875</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>1.06</v>
+        <v>1.1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>72</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3740,58 +3704,58 @@
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
       </c>
       <c r="V27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="b">
         <v>0</v>
       </c>
       <c r="X27">
-        <v>60.05</v>
+        <v>31.52</v>
       </c>
       <c r="Y27">
-        <v>148.74</v>
+        <v>49.3</v>
       </c>
       <c r="Z27">
-        <v>4.58</v>
+        <v>5.87</v>
       </c>
       <c r="AA27">
-        <v>-1031.14</v>
+        <v>14.02</v>
       </c>
       <c r="AB27">
-        <v>129.23</v>
+        <v>12.6</v>
       </c>
       <c r="AC27">
-        <v>60.87</v>
+        <v>61.4</v>
       </c>
       <c r="AD27">
-        <v>2.72</v>
+        <v>19.55</v>
       </c>
       <c r="AE27">
-        <v>-44.78</v>
+        <v>41.54</v>
       </c>
       <c r="AF27">
-        <v>204.55</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="AG27">
-        <v>-4.35</v>
+        <v>26.32</v>
       </c>
       <c r="AH27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="AJ27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AK27">
-        <v>34.42718599435409</v>
+        <v>37.07643812904068</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3799,109 +3763,109 @@
         <v>63</v>
       </c>
       <c r="B28">
-        <v>96.64551223934723</v>
+        <v>93.05653295801079</v>
       </c>
       <c r="C28">
-        <v>1570</v>
+        <v>993</v>
       </c>
       <c r="D28">
-        <v>137.14</v>
+        <v>15.68</v>
       </c>
       <c r="E28">
-        <v>0.6899999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="F28">
-        <v>-0.9374706375624308</v>
+        <v>0.3266286612840772</v>
       </c>
       <c r="G28">
-        <v>1.76</v>
+        <v>3.13</v>
       </c>
       <c r="H28">
-        <v>-0.2691620959210493</v>
+        <v>1.140549647705864</v>
       </c>
       <c r="I28">
-        <v>136.9779815673828</v>
+        <v>15.78800010681152</v>
       </c>
       <c r="J28">
-        <v>136.3718109130859</v>
+        <v>14.99499998092651</v>
       </c>
       <c r="K28">
-        <v>128.8716421508789</v>
+        <v>14.26699998855591</v>
       </c>
       <c r="L28">
-        <v>98.55812423706055</v>
+        <v>13.0752999830246</v>
       </c>
       <c r="M28">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="P28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>6.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
       </c>
       <c r="X28">
-        <v>70.92</v>
+        <v>8.9</v>
       </c>
       <c r="Y28">
-        <v>139.43</v>
+        <v>16.09</v>
       </c>
       <c r="Z28">
-        <v>14.38</v>
+        <v>1.57</v>
       </c>
       <c r="AA28">
-        <v>34.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AB28">
-        <v>1.18</v>
+        <v>44.44</v>
       </c>
       <c r="AC28">
-        <v>19.61</v>
+        <v>108.7</v>
       </c>
       <c r="AD28">
-        <v>5.42</v>
+        <v>0.27</v>
       </c>
       <c r="AE28">
-        <v>1.67</v>
+        <v>128.57</v>
       </c>
       <c r="AF28">
-        <v>17.65</v>
+        <v>-250</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>91.3</v>
       </c>
       <c r="AH28" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="AJ28" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AK28">
-        <v>34.14380923694621</v>
+        <v>35.59088572723824</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3909,49 +3873,49 @@
         <v>64</v>
       </c>
       <c r="B29">
-        <v>93.69900271985495</v>
+        <v>90.1946985690828</v>
       </c>
       <c r="C29">
-        <v>1202</v>
+        <v>1232</v>
       </c>
       <c r="D29">
-        <v>132.52</v>
+        <v>45.41</v>
       </c>
       <c r="E29">
-        <v>0.76</v>
+        <v>1.2</v>
       </c>
       <c r="F29">
-        <v>-0.8762425117419527</v>
+        <v>-0.9826697508518117</v>
       </c>
       <c r="G29">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="H29">
-        <v>-0.5316945835681809</v>
+        <v>-0.8979388424481374</v>
       </c>
       <c r="I29">
-        <v>134.7899993896484</v>
+        <v>45.72328491210938</v>
       </c>
       <c r="J29">
-        <v>135.9540008544922</v>
+        <v>44.03892192840576</v>
       </c>
       <c r="K29">
-        <v>128.6302006530762</v>
+        <v>42.8288077545166</v>
       </c>
       <c r="L29">
-        <v>107.0809501266479</v>
+        <v>41.59324760437012</v>
       </c>
       <c r="M29">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="N29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3960,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>0.5555555555555555</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="U29" t="b">
         <v>1</v>
@@ -3972,46 +3936,46 @@
         <v>1</v>
       </c>
       <c r="X29">
-        <v>79.14</v>
+        <v>31.98</v>
       </c>
       <c r="Y29">
-        <v>138.72</v>
+        <v>48.99</v>
       </c>
       <c r="Z29">
-        <v>18.63</v>
+        <v>4.02</v>
       </c>
       <c r="AA29">
-        <v>20.66</v>
+        <v>2.76</v>
       </c>
       <c r="AB29">
-        <v>240.34</v>
+        <v>217.8</v>
       </c>
       <c r="AC29">
-        <v>49.06</v>
+        <v>19.1</v>
       </c>
       <c r="AD29">
-        <v>3.02</v>
+        <v>1.98</v>
       </c>
       <c r="AE29">
-        <v>-23.3</v>
+        <v>-23.19</v>
       </c>
       <c r="AF29">
-        <v>-39.41</v>
+        <v>-49.64</v>
       </c>
       <c r="AG29">
-        <v>220.75</v>
+        <v>207.87</v>
       </c>
       <c r="AH29" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="AK29">
-        <v>33.89337467663286</v>
+        <v>34.01995447650669</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -4019,46 +3983,46 @@
         <v>65</v>
       </c>
       <c r="B30">
-        <v>98.09610154125113</v>
+        <v>96.83321604503871</v>
       </c>
       <c r="C30">
-        <v>590</v>
+        <v>1076</v>
       </c>
       <c r="D30">
-        <v>165.24</v>
+        <v>64.69</v>
       </c>
       <c r="E30">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="F30">
-        <v>0.007191875096373924</v>
+        <v>0.1688818646411992</v>
       </c>
       <c r="G30">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="H30">
-        <v>0.948033983170197</v>
+        <v>1.06153846591695</v>
       </c>
       <c r="I30">
-        <v>165.0179992675781</v>
+        <v>66.13600158691406</v>
       </c>
       <c r="J30">
-        <v>169.4274993896484</v>
+        <v>62.28050060272217</v>
       </c>
       <c r="K30">
-        <v>162.9101995849609</v>
+        <v>57.89900016784668</v>
       </c>
       <c r="L30">
-        <v>123.6735000610352</v>
+        <v>52.37995014190674</v>
       </c>
       <c r="M30">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="P30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -4070,58 +4034,58 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
       </c>
       <c r="V30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="b">
         <v>0</v>
       </c>
       <c r="X30">
-        <v>75.68000000000001</v>
+        <v>31.75</v>
       </c>
       <c r="Y30">
-        <v>176.9</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="Z30">
-        <v>22.09</v>
+        <v>2.22</v>
       </c>
       <c r="AA30">
-        <v>423.31</v>
+        <v>0.02</v>
       </c>
       <c r="AB30">
-        <v>21.09</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AC30">
-        <v>42.86</v>
+        <v>80</v>
       </c>
       <c r="AD30">
-        <v>5.5</v>
+        <v>3.44</v>
       </c>
       <c r="AE30">
-        <v>2.04</v>
+        <v>17.39</v>
       </c>
       <c r="AF30">
-        <v>11.36</v>
+        <v>12.2</v>
       </c>
       <c r="AG30">
-        <v>25.71</v>
+        <v>36.67</v>
       </c>
       <c r="AH30" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="AK30">
-        <v>31.92849107826805</v>
+        <v>33.54315435164126</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4129,43 +4093,43 @@
         <v>66</v>
       </c>
       <c r="B31">
-        <v>95.26291931097009</v>
+        <v>90.71076706544687</v>
       </c>
       <c r="C31">
-        <v>799</v>
+        <v>97</v>
       </c>
       <c r="D31">
-        <v>52.05</v>
+        <v>13.74</v>
       </c>
       <c r="E31">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="F31">
-        <v>0.1209012516201188</v>
+        <v>-0.41478128293745</v>
       </c>
       <c r="G31">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="H31">
-        <v>0.2678361742662653</v>
+        <v>-0.724114242512525</v>
       </c>
       <c r="I31">
-        <v>52.44200057983399</v>
+        <v>13.54540634155273</v>
       </c>
       <c r="J31">
-        <v>50.65099983215332</v>
+        <v>13.36329164505005</v>
       </c>
       <c r="K31">
-        <v>50.42979995727539</v>
+        <v>13.2782541847229</v>
       </c>
       <c r="L31">
-        <v>45.02414999961853</v>
+        <v>12.47465338230133</v>
       </c>
       <c r="M31">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -4189,49 +4153,49 @@
         <v>1</v>
       </c>
       <c r="W31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31">
-        <v>31.39</v>
+        <v>8.6</v>
       </c>
       <c r="Y31">
-        <v>56.1</v>
+        <v>14.74</v>
       </c>
       <c r="Z31">
-        <v>7.45</v>
+        <v>1.56</v>
       </c>
       <c r="AA31">
-        <v>-4.02</v>
+        <v>11.91</v>
       </c>
       <c r="AB31">
-        <v>180.95</v>
+        <v>11.86</v>
       </c>
       <c r="AC31">
-        <v>33.33</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="AD31">
-        <v>0.36</v>
+        <v>8.76</v>
       </c>
       <c r="AE31">
-        <v>-50</v>
+        <v>15.63</v>
       </c>
       <c r="AF31">
-        <v>300</v>
+        <v>-43.53</v>
       </c>
       <c r="AG31">
-        <v>-33.33</v>
+        <v>198.25</v>
       </c>
       <c r="AH31" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="AK31">
-        <v>29.88531819427674</v>
+        <v>31.74161269581864</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4239,46 +4203,46 @@
         <v>67</v>
       </c>
       <c r="B32">
-        <v>98.84406165004533</v>
+        <v>92.49354914379545</v>
       </c>
       <c r="C32">
-        <v>960</v>
+        <v>89</v>
       </c>
       <c r="D32">
-        <v>3.98</v>
+        <v>38.85</v>
       </c>
       <c r="E32">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="F32">
-        <v>-0.1852393774822714</v>
+        <v>-0.6514014779017676</v>
       </c>
       <c r="G32">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="H32">
-        <v>-0.2572288010279978</v>
+        <v>-0.04461807912785789</v>
       </c>
       <c r="I32">
-        <v>3.93534951210022</v>
+        <v>38.24599990844727</v>
       </c>
       <c r="J32">
-        <v>4.017451429367066</v>
+        <v>37.22249984741211</v>
       </c>
       <c r="K32">
-        <v>3.862705354690552</v>
+        <v>36.03079978942871</v>
       </c>
       <c r="L32">
-        <v>2.987582440376282</v>
+        <v>34.5838500213623</v>
       </c>
       <c r="M32">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="N32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -4290,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U32" t="b">
         <v>0</v>
@@ -4302,46 +4266,46 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>1.38</v>
+        <v>25.04</v>
       </c>
       <c r="Y32">
-        <v>4.23</v>
+        <v>39.44</v>
       </c>
       <c r="Z32">
-        <v>1.55</v>
+        <v>49.53</v>
       </c>
       <c r="AA32">
-        <v>9.529999999999999</v>
+        <v>242000</v>
       </c>
       <c r="AB32">
-        <v>5.42</v>
+        <v>303.33</v>
       </c>
       <c r="AC32">
-        <v>36.73</v>
+        <v>27.27</v>
       </c>
       <c r="AD32">
-        <v>3</v>
+        <v>4.42</v>
       </c>
       <c r="AE32">
-        <v>68.36</v>
+        <v>-9.68</v>
       </c>
       <c r="AF32">
-        <v>-13.08</v>
+        <v>-22.5</v>
       </c>
       <c r="AG32">
-        <v>-6.56</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AH32" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="AJ32" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="AK32">
-        <v>29.35209185387656</v>
+        <v>27.61803165141314</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4349,43 +4313,43 @@
         <v>68</v>
       </c>
       <c r="B33">
-        <v>95.58023572076156</v>
+        <v>93.17382125263899</v>
       </c>
       <c r="C33">
-        <v>1802</v>
+        <v>1898</v>
       </c>
       <c r="D33">
-        <v>53.67</v>
+        <v>66.5</v>
       </c>
       <c r="E33">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="F33">
-        <v>-0.5788487577567734</v>
+        <v>0.02690974766260903</v>
       </c>
       <c r="G33">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="H33">
-        <v>-0.5197612886751295</v>
+        <v>0.4294490116056313</v>
       </c>
       <c r="I33">
-        <v>54.9424545288086</v>
+        <v>67.46599884033203</v>
       </c>
       <c r="J33">
-        <v>53.76715621948242</v>
+        <v>65.51349983215331</v>
       </c>
       <c r="K33">
-        <v>52.17039970397949</v>
+        <v>59.73959991455078</v>
       </c>
       <c r="L33">
-        <v>45.03887407302857</v>
+        <v>55.88930000305176</v>
       </c>
       <c r="M33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N33">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4409,49 +4373,49 @@
         <v>0</v>
       </c>
       <c r="W33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33">
-        <v>31.82</v>
+        <v>42.11</v>
       </c>
       <c r="Y33">
-        <v>58.03</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Z33">
-        <v>2.94</v>
+        <v>2.17</v>
       </c>
       <c r="AA33">
-        <v>32.86</v>
+        <v>110.73</v>
       </c>
       <c r="AB33">
-        <v>11.93</v>
+        <v>26.32</v>
       </c>
       <c r="AC33">
-        <v>35</v>
+        <v>34.37</v>
       </c>
       <c r="AD33">
-        <v>3.07</v>
+        <v>4.82</v>
       </c>
       <c r="AE33">
-        <v>3.85</v>
+        <v>7.5</v>
       </c>
       <c r="AF33">
-        <v>1.96</v>
+        <v>37.93</v>
       </c>
       <c r="AG33">
-        <v>27.5</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AH33" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="AI33" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="AJ33" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="AK33">
-        <v>29.24833128890486</v>
+        <v>23.22311418807691</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4459,49 +4423,52 @@
         <v>69</v>
       </c>
       <c r="B34">
-        <v>92.95104261106074</v>
+        <v>91.69598874032371</v>
       </c>
       <c r="C34">
-        <v>805</v>
+        <v>1707</v>
       </c>
       <c r="D34">
-        <v>34.03</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="E34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="F34">
-        <v>-0.5875956328739845</v>
+        <v>-1.124641867830402</v>
       </c>
       <c r="G34">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="H34">
-        <v>-0.2691620959210493</v>
+        <v>-0.4870806971457805</v>
       </c>
       <c r="I34">
-        <v>34.11762161254883</v>
+        <v>86.18222045898438</v>
       </c>
       <c r="J34">
-        <v>33.5239278793335</v>
+        <v>81.03494377136231</v>
       </c>
       <c r="K34">
-        <v>32.35387462615967</v>
+        <v>79.59636413574219</v>
       </c>
       <c r="L34">
-        <v>28.92368920326233</v>
+        <v>79.5338659286499</v>
       </c>
       <c r="M34">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N34">
-        <v>1.05</v>
+        <v>1.08</v>
+      </c>
+      <c r="O34" t="s">
+        <v>71</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -4510,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="U34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="b">
         <v>1</v>
@@ -4522,46 +4489,46 @@
         <v>0</v>
       </c>
       <c r="X34">
-        <v>20.32</v>
+        <v>57.86</v>
       </c>
       <c r="Y34">
-        <v>34.68</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="Z34">
-        <v>5.24</v>
+        <v>11.37</v>
       </c>
       <c r="AA34">
-        <v>70.31</v>
+        <v>39.33</v>
       </c>
       <c r="AB34">
-        <v>268.18</v>
+        <v>3.16</v>
       </c>
       <c r="AC34">
-        <v>28.57</v>
+        <v>4.08</v>
       </c>
       <c r="AD34">
-        <v>2.85</v>
+        <v>4.93</v>
       </c>
       <c r="AE34">
-        <v>-47.06</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>126.67</v>
+        <v>13.33</v>
       </c>
       <c r="AG34">
-        <v>7.14</v>
+        <v>-8.16</v>
       </c>
       <c r="AH34" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="AJ34" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="AK34">
-        <v>28.85203265305826</v>
+        <v>14.3190868882318</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -4569,49 +4536,49 @@
         <v>70</v>
       </c>
       <c r="B35">
-        <v>90.00453309156845</v>
+        <v>92.63429509734928</v>
       </c>
       <c r="C35">
-        <v>1811</v>
+        <v>698</v>
       </c>
       <c r="D35">
-        <v>9.5</v>
+        <v>39.86</v>
       </c>
       <c r="E35">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="F35">
-        <v>-1.033686263851753</v>
+        <v>-1.235064625480417</v>
       </c>
       <c r="G35">
-        <v>0.65</v>
+        <v>1.55</v>
       </c>
       <c r="H35">
-        <v>-1.593757829049759</v>
+        <v>-1.356203696823843</v>
       </c>
       <c r="I35">
-        <v>9.433235168457033</v>
+        <v>39.82717132568359</v>
       </c>
       <c r="J35">
-        <v>9.382090330123903</v>
+        <v>38.08821315765381</v>
       </c>
       <c r="K35">
-        <v>9.151575832366943</v>
+        <v>37.14229042053223</v>
       </c>
       <c r="L35">
-        <v>8.253476669788361</v>
+        <v>33.52940236091614</v>
       </c>
       <c r="M35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N35">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -4620,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="T35">
-        <v>2.222222222222222</v>
+        <v>0</v>
       </c>
       <c r="U35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" t="b">
         <v>1</v>
@@ -4632,1256 +4599,46 @@
         <v>0</v>
       </c>
       <c r="X35">
-        <v>6.98</v>
+        <v>26.04</v>
       </c>
       <c r="Y35">
-        <v>9.529999999999999</v>
+        <v>40.36</v>
       </c>
       <c r="Z35">
-        <v>4.15</v>
+        <v>5.19</v>
       </c>
       <c r="AA35">
-        <v>231.29</v>
+        <v>18.42</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>5.52</v>
       </c>
       <c r="AC35">
-        <v>21.43</v>
+        <v>11.9</v>
       </c>
       <c r="AD35">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AE35">
-        <v>112.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF35">
-        <v>-33.33</v>
+        <v>-35.48</v>
       </c>
       <c r="AG35">
-        <v>-14.29</v>
+        <v>47.62</v>
       </c>
       <c r="AH35" t="s">
         <v>86</v>
       </c>
       <c r="AI35" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="AJ35" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="AK35">
-        <v>28.5735053780485</v>
-      </c>
-    </row>
-    <row r="36" spans="1:37">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36">
-        <v>94.58295557570263</v>
-      </c>
-      <c r="C36">
-        <v>959</v>
-      </c>
-      <c r="D36">
-        <v>89.59</v>
-      </c>
-      <c r="E36">
-        <v>1.82</v>
-      </c>
-      <c r="F36">
-        <v>0.05092625068242973</v>
-      </c>
-      <c r="G36">
-        <v>2.75</v>
-      </c>
-      <c r="H36">
-        <v>0.912234098491043</v>
-      </c>
-      <c r="I36">
-        <v>90.2759994506836</v>
-      </c>
-      <c r="J36">
-        <v>89.84850006103515</v>
-      </c>
-      <c r="K36">
-        <v>85.47039993286133</v>
-      </c>
-      <c r="L36">
-        <v>76.52535020828248</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36">
-        <v>1.06</v>
-      </c>
-      <c r="P36">
-        <v>1</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0.5555555555555555</v>
-      </c>
-      <c r="U36" t="b">
-        <v>0</v>
-      </c>
-      <c r="V36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W36" t="b">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>53.21</v>
-      </c>
-      <c r="Y36">
-        <v>94.52</v>
-      </c>
-      <c r="Z36">
-        <v>16.62</v>
-      </c>
-      <c r="AA36">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="AB36">
-        <v>29.2</v>
-      </c>
-      <c r="AC36">
-        <v>26.56</v>
-      </c>
-      <c r="AD36">
-        <v>5.47</v>
-      </c>
-      <c r="AE36">
-        <v>32.79</v>
-      </c>
-      <c r="AF36">
-        <v>201.67</v>
-      </c>
-      <c r="AG36">
-        <v>-193.75</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK36">
-        <v>28.36444615582292</v>
-      </c>
-    </row>
-    <row r="37" spans="1:37">
-      <c r="A37" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37">
-        <v>98.95738893925657</v>
-      </c>
-      <c r="C37">
-        <v>217</v>
-      </c>
-      <c r="D37">
-        <v>19.3</v>
-      </c>
-      <c r="E37">
-        <v>4.28</v>
-      </c>
-      <c r="F37">
-        <v>2.202657529516374</v>
-      </c>
-      <c r="G37">
-        <v>3.71</v>
-      </c>
-      <c r="H37">
-        <v>2.057830408223981</v>
-      </c>
-      <c r="I37">
-        <v>17.62199974060059</v>
-      </c>
-      <c r="J37">
-        <v>16.52149991989136</v>
-      </c>
-      <c r="K37">
-        <v>14.87759998321533</v>
-      </c>
-      <c r="L37">
-        <v>10.82924999952316</v>
-      </c>
-      <c r="M37">
-        <v>1.07</v>
-      </c>
-      <c r="N37">
-        <v>1.18</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>1</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="U37" t="b">
-        <v>0</v>
-      </c>
-      <c r="V37" t="b">
-        <v>1</v>
-      </c>
-      <c r="W37" t="b">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>5.38</v>
-      </c>
-      <c r="Y37">
-        <v>20.9</v>
-      </c>
-      <c r="Z37">
-        <v>2</v>
-      </c>
-      <c r="AA37">
-        <v>14.28</v>
-      </c>
-      <c r="AB37">
-        <v>121.05</v>
-      </c>
-      <c r="AC37">
-        <v>20</v>
-      </c>
-      <c r="AD37">
-        <v>2.9</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>220</v>
-      </c>
-      <c r="AG37">
-        <v>-200</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI37" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK37">
-        <v>27.65355756497783</v>
-      </c>
-    </row>
-    <row r="38" spans="1:37">
-      <c r="A38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38">
-        <v>97.21214868540345</v>
-      </c>
-      <c r="C38">
-        <v>514</v>
-      </c>
-      <c r="D38">
-        <v>32.34</v>
-      </c>
-      <c r="E38">
-        <v>3.91</v>
-      </c>
-      <c r="F38">
-        <v>1.879023150179561</v>
-      </c>
-      <c r="G38">
-        <v>3.53</v>
-      </c>
-      <c r="H38">
-        <v>1.843031100149055</v>
-      </c>
-      <c r="I38">
-        <v>34.83399963378906</v>
-      </c>
-      <c r="J38">
-        <v>33.58599967956543</v>
-      </c>
-      <c r="K38">
-        <v>29.55239997863769</v>
-      </c>
-      <c r="L38">
-        <v>25.57178441057212</v>
-      </c>
-      <c r="M38">
-        <v>1.04</v>
-      </c>
-      <c r="N38">
-        <v>1.18</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38" t="b">
-        <v>0</v>
-      </c>
-      <c r="V38" t="b">
-        <v>0</v>
-      </c>
-      <c r="W38" t="b">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>12.4</v>
-      </c>
-      <c r="Y38">
-        <v>38.11</v>
-      </c>
-      <c r="Z38">
-        <v>2.5</v>
-      </c>
-      <c r="AA38">
-        <v>0.16</v>
-      </c>
-      <c r="AB38">
-        <v>50</v>
-      </c>
-      <c r="AC38">
-        <v>23.81</v>
-      </c>
-      <c r="AD38">
-        <v>34.75</v>
-      </c>
-      <c r="AE38">
-        <v>766.67</v>
-      </c>
-      <c r="AF38">
-        <v>-90.31999999999999</v>
-      </c>
-      <c r="AG38">
-        <v>47.62</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>144</v>
-      </c>
-      <c r="AK38">
-        <v>26.82277045174635</v>
-      </c>
-    </row>
-    <row r="39" spans="1:37">
-      <c r="A39" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39">
-        <v>90.23118766999093</v>
-      </c>
-      <c r="C39">
-        <v>1150</v>
-      </c>
-      <c r="D39">
-        <v>40.94</v>
-      </c>
-      <c r="E39">
-        <v>1.23</v>
-      </c>
-      <c r="F39">
-        <v>-0.4651393812330284</v>
-      </c>
-      <c r="G39">
-        <v>0.96</v>
-      </c>
-      <c r="H39">
-        <v>-1.223825687365164</v>
-      </c>
-      <c r="I39">
-        <v>39.76022872924805</v>
-      </c>
-      <c r="J39">
-        <v>38.63883323669434</v>
-      </c>
-      <c r="K39">
-        <v>38.06994110107422</v>
-      </c>
-      <c r="L39">
-        <v>34.29715715408325</v>
-      </c>
-      <c r="M39">
-        <v>1.03</v>
-      </c>
-      <c r="N39">
-        <v>1.04</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39" t="b">
-        <v>0</v>
-      </c>
-      <c r="V39" t="b">
-        <v>1</v>
-      </c>
-      <c r="W39" t="b">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>27.93</v>
-      </c>
-      <c r="Y39">
-        <v>41.24</v>
-      </c>
-      <c r="Z39">
-        <v>10.73</v>
-      </c>
-      <c r="AA39">
-        <v>-16.85</v>
-      </c>
-      <c r="AB39">
-        <v>0.46</v>
-      </c>
-      <c r="AC39">
-        <v>24.18</v>
-      </c>
-      <c r="AD39">
-        <v>5.83</v>
-      </c>
-      <c r="AE39">
-        <v>56.52</v>
-      </c>
-      <c r="AF39">
-        <v>15</v>
-      </c>
-      <c r="AG39">
-        <v>-40.48</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>103</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>120</v>
-      </c>
-      <c r="AK39">
-        <v>25.57802469358369</v>
-      </c>
-    </row>
-    <row r="40" spans="1:37">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40">
-        <v>94.67361740707162</v>
-      </c>
-      <c r="C40">
-        <v>1312</v>
-      </c>
-      <c r="D40">
-        <v>34.71</v>
-      </c>
-      <c r="E40">
-        <v>3</v>
-      </c>
-      <c r="F40">
-        <v>1.083057514513346</v>
-      </c>
-      <c r="G40">
-        <v>2.1</v>
-      </c>
-      <c r="H40">
-        <v>0.1365699304426997</v>
-      </c>
-      <c r="I40">
-        <v>31.4518367767334</v>
-      </c>
-      <c r="J40">
-        <v>31.50808696746826</v>
-      </c>
-      <c r="K40">
-        <v>30.01143466949463</v>
-      </c>
-      <c r="L40">
-        <v>27.79108713150024</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40">
-        <v>1.05</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40" t="b">
-        <v>0</v>
-      </c>
-      <c r="V40" t="b">
-        <v>1</v>
-      </c>
-      <c r="W40" t="b">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>21.62</v>
-      </c>
-      <c r="Y40">
-        <v>36.25</v>
-      </c>
-      <c r="Z40">
-        <v>2.32</v>
-      </c>
-      <c r="AA40">
-        <v>22.15</v>
-      </c>
-      <c r="AB40">
-        <v>24.07</v>
-      </c>
-      <c r="AC40">
-        <v>18.75</v>
-      </c>
-      <c r="AD40">
-        <v>11.86</v>
-      </c>
-      <c r="AE40">
-        <v>2.7</v>
-      </c>
-      <c r="AF40">
-        <v>37.04</v>
-      </c>
-      <c r="AG40">
-        <v>-15.62</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK40">
-        <v>24.74209038866767</v>
-      </c>
-    </row>
-    <row r="41" spans="1:37">
-      <c r="A41" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41">
-        <v>95.73889392565729</v>
-      </c>
-      <c r="C41">
-        <v>1562</v>
-      </c>
-      <c r="D41">
-        <v>105.31</v>
-      </c>
-      <c r="E41">
-        <v>0.91</v>
-      </c>
-      <c r="F41">
-        <v>-0.7450393849837853</v>
-      </c>
-      <c r="G41">
-        <v>1.62</v>
-      </c>
-      <c r="H41">
-        <v>-0.4362282244237693</v>
-      </c>
-      <c r="I41">
-        <v>105.9490325927734</v>
-      </c>
-      <c r="J41">
-        <v>106.335075378418</v>
-      </c>
-      <c r="K41">
-        <v>101.6982055664062</v>
-      </c>
-      <c r="L41">
-        <v>80.55616804122924</v>
-      </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-      <c r="N41">
-        <v>1.04</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41" t="b">
-        <v>1</v>
-      </c>
-      <c r="V41" t="b">
-        <v>0</v>
-      </c>
-      <c r="W41" t="b">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>57.3</v>
-      </c>
-      <c r="Y41">
-        <v>108.56</v>
-      </c>
-      <c r="Z41">
-        <v>12.17</v>
-      </c>
-      <c r="AA41">
-        <v>34.52</v>
-      </c>
-      <c r="AB41">
-        <v>1.18</v>
-      </c>
-      <c r="AC41">
-        <v>19.61</v>
-      </c>
-      <c r="AD41">
-        <v>5.42</v>
-      </c>
-      <c r="AE41">
-        <v>1.67</v>
-      </c>
-      <c r="AF41">
-        <v>17.65</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK41">
-        <v>24.14380923694621</v>
-      </c>
-    </row>
-    <row r="42" spans="1:37">
-      <c r="A42" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42">
-        <v>94.42429737080688</v>
-      </c>
-      <c r="C42">
-        <v>2406</v>
-      </c>
-      <c r="D42">
-        <v>88.98</v>
-      </c>
-      <c r="E42">
-        <v>1.56</v>
-      </c>
-      <c r="F42">
-        <v>-0.1764925023650603</v>
-      </c>
-      <c r="G42">
-        <v>1.64</v>
-      </c>
-      <c r="H42">
-        <v>-0.4123616346376667</v>
-      </c>
-      <c r="I42">
-        <v>88.87442779541016</v>
-      </c>
-      <c r="J42">
-        <v>91.34700164794921</v>
-      </c>
-      <c r="K42">
-        <v>88.62280090332031</v>
-      </c>
-      <c r="L42">
-        <v>69.54897708892823</v>
-      </c>
-      <c r="M42">
-        <v>0.97</v>
-      </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
-      <c r="P42">
-        <v>1</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0.5555555555555555</v>
-      </c>
-      <c r="U42" t="b">
-        <v>1</v>
-      </c>
-      <c r="V42" t="b">
-        <v>1</v>
-      </c>
-      <c r="W42" t="b">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>49.67</v>
-      </c>
-      <c r="Y42">
-        <v>98.59</v>
-      </c>
-      <c r="Z42">
-        <v>1.97</v>
-      </c>
-      <c r="AA42" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB42">
-        <v>22.34</v>
-      </c>
-      <c r="AC42">
-        <v>14.04</v>
-      </c>
-      <c r="AD42">
-        <v>4.47</v>
-      </c>
-      <c r="AE42">
-        <v>-26.14</v>
-      </c>
-      <c r="AF42">
-        <v>340</v>
-      </c>
-      <c r="AG42">
-        <v>-64.91</v>
-      </c>
-      <c r="AH42" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>145</v>
-      </c>
-      <c r="AK42">
-        <v>23.46370591700445</v>
-      </c>
-    </row>
-    <row r="43" spans="1:37">
-      <c r="A43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43">
-        <v>91.4324569356301</v>
-      </c>
-      <c r="C43">
-        <v>255</v>
-      </c>
-      <c r="D43">
-        <v>266.28</v>
-      </c>
-      <c r="E43">
-        <v>0.83</v>
-      </c>
-      <c r="F43">
-        <v>-0.8150143859214746</v>
-      </c>
-      <c r="G43">
-        <v>1.28</v>
-      </c>
-      <c r="H43">
-        <v>-0.8419602507875182</v>
-      </c>
-      <c r="I43">
-        <v>269.6371948242187</v>
-      </c>
-      <c r="J43">
-        <v>268.9646057128906</v>
-      </c>
-      <c r="K43">
-        <v>258.6940835571289</v>
-      </c>
-      <c r="L43">
-        <v>221.1240334320068</v>
-      </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-      <c r="N43">
-        <v>1.04</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>1</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="U43" t="b">
-        <v>1</v>
-      </c>
-      <c r="V43" t="b">
-        <v>0</v>
-      </c>
-      <c r="W43" t="b">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>166.23</v>
-      </c>
-      <c r="Y43">
-        <v>275.18</v>
-      </c>
-      <c r="Z43">
-        <v>263.03</v>
-      </c>
-      <c r="AA43">
-        <v>9.75</v>
-      </c>
-      <c r="AB43">
-        <v>3.32</v>
-      </c>
-      <c r="AC43">
-        <v>9.84</v>
-      </c>
-      <c r="AD43">
-        <v>40.68</v>
-      </c>
-      <c r="AE43">
-        <v>11.05</v>
-      </c>
-      <c r="AF43">
-        <v>105.68</v>
-      </c>
-      <c r="AG43">
-        <v>-51.91</v>
-      </c>
-      <c r="AH43" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI43" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ43" t="s">
-        <v>146</v>
-      </c>
-      <c r="AK43">
-        <v>21.12977772888731</v>
-      </c>
-    </row>
-    <row r="44" spans="1:37">
-      <c r="A44" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44">
-        <v>96.96282864913871</v>
-      </c>
-      <c r="C44">
-        <v>837</v>
-      </c>
-      <c r="D44">
-        <v>25.85</v>
-      </c>
-      <c r="E44">
-        <v>2.47</v>
-      </c>
-      <c r="F44">
-        <v>0.6194731333011548</v>
-      </c>
-      <c r="G44">
-        <v>2.45</v>
-      </c>
-      <c r="H44">
-        <v>0.5542352516995001</v>
-      </c>
-      <c r="I44">
-        <v>24.37799987792969</v>
-      </c>
-      <c r="J44">
-        <v>23.42849988937378</v>
-      </c>
-      <c r="K44">
-        <v>22.86819999694824</v>
-      </c>
-      <c r="L44">
-        <v>18.87324995517731</v>
-      </c>
-      <c r="M44">
-        <v>1.04</v>
-      </c>
-      <c r="N44">
-        <v>1.07</v>
-      </c>
-      <c r="P44">
-        <v>1</v>
-      </c>
-      <c r="Q44">
-        <v>2</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>2.777777777777778</v>
-      </c>
-      <c r="U44" t="b">
-        <v>0</v>
-      </c>
-      <c r="V44" t="b">
-        <v>1</v>
-      </c>
-      <c r="W44" t="b">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>11.05</v>
-      </c>
-      <c r="Y44">
-        <v>25.98</v>
-      </c>
-      <c r="Z44">
-        <v>2.25</v>
-      </c>
-      <c r="AA44">
-        <v>444.44</v>
-      </c>
-      <c r="AB44">
-        <v>1.441151880758558E+17</v>
-      </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
-      <c r="AD44">
-        <v>0.41</v>
-      </c>
-      <c r="AE44">
-        <v>166.67</v>
-      </c>
-      <c r="AF44">
-        <v>-400</v>
-      </c>
-      <c r="AG44">
-        <v>-50</v>
-      </c>
-      <c r="AH44" t="s">
-        <v>88</v>
-      </c>
-      <c r="AI44" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ44" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK44">
-        <v>19.54545454545454</v>
-      </c>
-    </row>
-    <row r="45" spans="1:37">
-      <c r="A45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45">
-        <v>95.89755213055304</v>
-      </c>
-      <c r="C45">
-        <v>630</v>
-      </c>
-      <c r="D45">
-        <v>73.04000000000001</v>
-      </c>
-      <c r="E45">
-        <v>1.13</v>
-      </c>
-      <c r="F45">
-        <v>-0.5526081324051401</v>
-      </c>
-      <c r="G45">
-        <v>1.7</v>
-      </c>
-      <c r="H45">
-        <v>-0.340761865279358</v>
-      </c>
-      <c r="I45">
-        <v>74.9500015258789</v>
-      </c>
-      <c r="J45">
-        <v>74.69900016784668</v>
-      </c>
-      <c r="K45">
-        <v>70.56179977416993</v>
-      </c>
-      <c r="L45">
-        <v>57.363099899292</v>
-      </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-      <c r="N45">
-        <v>1.06</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45" t="b">
-        <v>1</v>
-      </c>
-      <c r="V45" t="b">
-        <v>0</v>
-      </c>
-      <c r="W45" t="b">
-        <v>1</v>
-      </c>
-      <c r="X45">
-        <v>39.08</v>
-      </c>
-      <c r="Y45">
-        <v>77.08</v>
-      </c>
-      <c r="Z45">
-        <v>19.9</v>
-      </c>
-      <c r="AA45">
-        <v>86.11</v>
-      </c>
-      <c r="AB45">
-        <v>34.78</v>
-      </c>
-      <c r="AC45">
-        <v>8.33</v>
-      </c>
-      <c r="AD45">
-        <v>7.5</v>
-      </c>
-      <c r="AE45">
-        <v>-11.36</v>
-      </c>
-      <c r="AF45">
-        <v>22.22</v>
-      </c>
-      <c r="AG45">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="s">
-        <v>104</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK45">
-        <v>18.93265146455037</v>
-      </c>
-    </row>
-    <row r="46" spans="1:37">
-      <c r="A46" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46">
-        <v>94.60562103354488</v>
-      </c>
-      <c r="C46">
-        <v>863</v>
-      </c>
-      <c r="D46">
-        <v>185.45</v>
-      </c>
-      <c r="E46">
-        <v>1.31</v>
-      </c>
-      <c r="F46">
-        <v>-0.3951643802953391</v>
-      </c>
-      <c r="G46">
-        <v>1.83</v>
-      </c>
-      <c r="H46">
-        <v>-0.1856290316696892</v>
-      </c>
-      <c r="I46">
-        <v>190.2019989013672</v>
-      </c>
-      <c r="J46">
-        <v>188.5415016174316</v>
-      </c>
-      <c r="K46">
-        <v>180.7516012573242</v>
-      </c>
-      <c r="L46">
-        <v>155.4579503631592</v>
-      </c>
-      <c r="M46">
-        <v>1.01</v>
-      </c>
-      <c r="N46">
-        <v>1.05</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46" t="b">
-        <v>1</v>
-      </c>
-      <c r="V46" t="b">
-        <v>0</v>
-      </c>
-      <c r="W46" t="b">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>110.71</v>
-      </c>
-      <c r="Y46">
-        <v>194.25</v>
-      </c>
-      <c r="Z46">
-        <v>23.16</v>
-      </c>
-      <c r="AA46">
-        <v>17.83</v>
-      </c>
-      <c r="AB46">
-        <v>30.38</v>
-      </c>
-      <c r="AC46">
-        <v>4.23</v>
-      </c>
-      <c r="AD46">
-        <v>7.07</v>
-      </c>
-      <c r="AE46">
-        <v>-55.42</v>
-      </c>
-      <c r="AF46">
-        <v>133.8</v>
-      </c>
-      <c r="AG46">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI46" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ46" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK46">
-        <v>14.29309627174952</v>
+        <v>10.27606078503347</v>
       </c>
     </row>
   </sheetData>
